--- a/sampledata/Bookmaster.xlsx
+++ b/sampledata/Bookmaster.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="I:\RLLT\Webapp\sampledata\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DA86CA45-B8D4-48AC-9A84-A553B08C3A90}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E6ADDF02-5B20-4410-9419-F5BF2BDFA95F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4692" yWindow="6144" windowWidth="17280" windowHeight="5784" xr2:uid="{A63EC1BA-E482-4B3F-96BC-8F4353DAA050}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{A63EC1BA-E482-4B3F-96BC-8F4353DAA050}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="336" uniqueCount="187">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="403" uniqueCount="190">
   <si>
     <t>Author</t>
   </si>
@@ -971,6 +971,15 @@
   </si>
   <si>
     <t>Total ART</t>
+  </si>
+  <si>
+    <t>BookType</t>
+  </si>
+  <si>
+    <t>OLD  TESTAMENT - OT BKS</t>
+  </si>
+  <si>
+    <t>NEW TESTAMENT - NT BKS</t>
   </si>
 </sst>
 </file>
@@ -1388,17 +1397,18 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{66F16A48-E642-407B-865B-40ED60A40CB0}">
-  <dimension ref="A1:G67"/>
+  <dimension ref="A1:H67"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="18.44140625" style="1" customWidth="1"/>
     <col min="2" max="2" width="18.5546875" style="1" customWidth="1"/>
     <col min="3" max="3" width="12.88671875" customWidth="1"/>
-    <col min="4" max="4" width="16.33203125" customWidth="1"/>
-    <col min="5" max="5" width="13.5546875" customWidth="1"/>
+    <col min="4" max="4" width="23.77734375" customWidth="1"/>
+    <col min="5" max="5" width="16.33203125" customWidth="1"/>
+    <col min="6" max="6" width="13.5546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1" s="6" t="s">
         <v>184</v>
       </c>
@@ -1409,19 +1419,22 @@
         <v>0</v>
       </c>
       <c r="D1" s="7" t="s">
+        <v>187</v>
+      </c>
+      <c r="E1" s="7" t="s">
         <v>182</v>
       </c>
-      <c r="E1" s="7" t="s">
+      <c r="F1" s="7" t="s">
         <v>183</v>
       </c>
-      <c r="F1" s="7" t="s">
+      <c r="G1" s="7" t="s">
         <v>186</v>
       </c>
-      <c r="G1" s="7" t="s">
+      <c r="H1" s="7" t="s">
         <v>181</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:8" ht="25.2" x14ac:dyDescent="0.3">
       <c r="A2" s="3" t="s">
         <v>1</v>
       </c>
@@ -1431,20 +1444,23 @@
       <c r="C2" s="8" t="s">
         <v>133</v>
       </c>
-      <c r="D2" s="5">
+      <c r="D2" s="8" t="s">
+        <v>188</v>
+      </c>
+      <c r="E2" s="5">
         <v>50</v>
       </c>
-      <c r="E2" s="5">
+      <c r="F2" s="5">
         <v>1533</v>
       </c>
-      <c r="F2" s="4" t="s">
+      <c r="G2" s="4" t="s">
         <v>152</v>
       </c>
-      <c r="G2" s="2" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H2" s="2" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A3" s="3" t="s">
         <v>2</v>
       </c>
@@ -1454,20 +1470,23 @@
       <c r="C3" s="2" t="s">
         <v>180</v>
       </c>
-      <c r="D3" s="5">
+      <c r="D3" s="8" t="s">
+        <v>188</v>
+      </c>
+      <c r="E3" s="5">
         <v>40</v>
       </c>
-      <c r="E3" s="5">
+      <c r="F3" s="5">
         <v>1213</v>
       </c>
-      <c r="F3" s="4" t="s">
+      <c r="G3" s="4" t="s">
         <v>153</v>
       </c>
-      <c r="G3" s="2" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H3" s="2" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A4" s="3" t="s">
         <v>3</v>
       </c>
@@ -1477,20 +1496,23 @@
       <c r="C4" s="2" t="s">
         <v>180</v>
       </c>
-      <c r="D4" s="5">
+      <c r="D4" s="8" t="s">
+        <v>188</v>
+      </c>
+      <c r="E4" s="5">
         <v>27</v>
       </c>
-      <c r="E4" s="5">
+      <c r="F4" s="5">
         <v>859</v>
       </c>
-      <c r="F4" s="4" t="s">
+      <c r="G4" s="4" t="s">
         <v>153</v>
       </c>
-      <c r="G4" s="2" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H4" s="2" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A5" s="3" t="s">
         <v>4</v>
       </c>
@@ -1500,20 +1522,23 @@
       <c r="C5" s="2" t="s">
         <v>180</v>
       </c>
-      <c r="D5" s="5">
+      <c r="D5" s="8" t="s">
+        <v>188</v>
+      </c>
+      <c r="E5" s="5">
         <v>36</v>
       </c>
-      <c r="E5" s="5">
+      <c r="F5" s="5">
         <v>1288</v>
       </c>
-      <c r="F5" s="4" t="s">
+      <c r="G5" s="4" t="s">
         <v>153</v>
       </c>
-      <c r="G5" s="2" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H5" s="2" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A6" s="3" t="s">
         <v>5</v>
       </c>
@@ -1523,20 +1548,23 @@
       <c r="C6" s="2" t="s">
         <v>180</v>
       </c>
-      <c r="D6" s="5">
+      <c r="D6" s="8" t="s">
+        <v>188</v>
+      </c>
+      <c r="E6" s="5">
         <v>34</v>
       </c>
-      <c r="E6" s="5">
+      <c r="F6" s="5">
         <v>958</v>
       </c>
-      <c r="F6" s="4" t="s">
+      <c r="G6" s="4" t="s">
         <v>154</v>
       </c>
-      <c r="G6" s="2" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H6" s="2" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A7" s="3" t="s">
         <v>6</v>
       </c>
@@ -1546,20 +1574,23 @@
       <c r="C7" s="8" t="s">
         <v>134</v>
       </c>
-      <c r="D7" s="5">
+      <c r="D7" s="8" t="s">
+        <v>188</v>
+      </c>
+      <c r="E7" s="5">
         <v>24</v>
       </c>
-      <c r="E7" s="5">
+      <c r="F7" s="5">
         <v>658</v>
       </c>
-      <c r="F7" s="4" t="s">
+      <c r="G7" s="4" t="s">
         <v>155</v>
       </c>
-      <c r="G7" s="2" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H7" s="2" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A8" s="3" t="s">
         <v>7</v>
       </c>
@@ -1569,20 +1600,23 @@
       <c r="C8" s="8" t="s">
         <v>135</v>
       </c>
-      <c r="D8" s="5">
+      <c r="D8" s="8" t="s">
+        <v>188</v>
+      </c>
+      <c r="E8" s="5">
         <v>21</v>
       </c>
-      <c r="E8" s="5">
+      <c r="F8" s="5">
         <v>681</v>
       </c>
-      <c r="F8" s="4" t="s">
+      <c r="G8" s="4" t="s">
         <v>156</v>
       </c>
-      <c r="G8" s="2" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H8" s="2" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A9" s="3" t="s">
         <v>8</v>
       </c>
@@ -1592,20 +1626,23 @@
       <c r="C9" s="2" t="s">
         <v>180</v>
       </c>
-      <c r="D9" s="5">
+      <c r="D9" s="8" t="s">
+        <v>188</v>
+      </c>
+      <c r="E9" s="5">
         <v>4</v>
       </c>
-      <c r="E9" s="5">
+      <c r="F9" s="5">
         <v>85</v>
       </c>
-      <c r="F9" s="4" t="s">
+      <c r="G9" s="4" t="s">
         <v>157</v>
       </c>
-      <c r="G9" s="2" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H9" s="2" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A10" s="3" t="s">
         <v>9</v>
       </c>
@@ -1615,20 +1652,23 @@
       <c r="C10" s="2" t="s">
         <v>180</v>
       </c>
-      <c r="D10" s="5">
+      <c r="D10" s="8" t="s">
+        <v>188</v>
+      </c>
+      <c r="E10" s="5">
         <v>31</v>
       </c>
-      <c r="E10" s="5">
+      <c r="F10" s="5">
         <v>810</v>
       </c>
-      <c r="F10" s="4" t="s">
+      <c r="G10" s="4" t="s">
         <v>158</v>
       </c>
-      <c r="G10" s="2" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H10" s="2" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A11" s="3" t="s">
         <v>10</v>
       </c>
@@ -1638,20 +1678,23 @@
       <c r="C11" s="2" t="s">
         <v>180</v>
       </c>
-      <c r="D11" s="5">
+      <c r="D11" s="8" t="s">
+        <v>188</v>
+      </c>
+      <c r="E11" s="5">
         <v>24</v>
       </c>
-      <c r="E11" s="5">
+      <c r="F11" s="5">
         <v>695</v>
       </c>
-      <c r="F11" s="4" t="s">
+      <c r="G11" s="4" t="s">
         <v>159</v>
       </c>
-      <c r="G11" s="2" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H11" s="2" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A12" s="3" t="s">
         <v>11</v>
       </c>
@@ -1661,20 +1704,23 @@
       <c r="C12" s="8" t="s">
         <v>136</v>
       </c>
-      <c r="D12" s="5">
+      <c r="D12" s="8" t="s">
+        <v>188</v>
+      </c>
+      <c r="E12" s="5">
         <v>22</v>
       </c>
-      <c r="E12" s="5">
+      <c r="F12" s="5">
         <v>816</v>
       </c>
-      <c r="F12" s="4" t="s">
+      <c r="G12" s="4" t="s">
         <v>160</v>
       </c>
-      <c r="G12" s="2" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H12" s="2" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A13" s="3" t="s">
         <v>12</v>
       </c>
@@ -1684,20 +1730,23 @@
       <c r="C13" s="2" t="s">
         <v>180</v>
       </c>
-      <c r="D13" s="5">
+      <c r="D13" s="8" t="s">
+        <v>188</v>
+      </c>
+      <c r="E13" s="5">
         <v>25</v>
       </c>
-      <c r="E13" s="5">
+      <c r="F13" s="5">
         <v>719</v>
       </c>
-      <c r="F13" s="4" t="s">
+      <c r="G13" s="4" t="s">
         <v>158</v>
       </c>
-      <c r="G13" s="2" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H13" s="2" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A14" s="3" t="s">
         <v>13</v>
       </c>
@@ -1707,20 +1756,23 @@
       <c r="C14" s="8" t="s">
         <v>137</v>
       </c>
-      <c r="D14" s="5">
+      <c r="D14" s="8" t="s">
+        <v>188</v>
+      </c>
+      <c r="E14" s="5">
         <v>29</v>
       </c>
-      <c r="E14" s="5">
+      <c r="F14" s="5">
         <v>942</v>
       </c>
-      <c r="F14" s="4" t="s">
+      <c r="G14" s="4" t="s">
         <v>161</v>
       </c>
-      <c r="G14" s="2" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H14" s="2" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A15" s="3" t="s">
         <v>14</v>
       </c>
@@ -1730,20 +1782,23 @@
       <c r="C15" s="2" t="s">
         <v>180</v>
       </c>
-      <c r="D15" s="5">
+      <c r="D15" s="8" t="s">
+        <v>188</v>
+      </c>
+      <c r="E15" s="5">
         <v>36</v>
       </c>
-      <c r="E15" s="5">
+      <c r="F15" s="5">
         <v>822</v>
       </c>
-      <c r="F15" s="4" t="s">
+      <c r="G15" s="4" t="s">
         <v>154</v>
       </c>
-      <c r="G15" s="2" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H15" s="2" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A16" s="3" t="s">
         <v>15</v>
       </c>
@@ -1753,20 +1808,23 @@
       <c r="C16" s="2" t="s">
         <v>180</v>
       </c>
-      <c r="D16" s="5">
+      <c r="D16" s="8" t="s">
+        <v>188</v>
+      </c>
+      <c r="E16" s="5">
         <v>10</v>
       </c>
-      <c r="E16" s="5">
+      <c r="F16" s="5">
         <v>280</v>
       </c>
-      <c r="F16" s="4" t="s">
+      <c r="G16" s="4" t="s">
         <v>162</v>
       </c>
-      <c r="G16" s="2" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H16" s="2" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A17" s="3" t="s">
         <v>16</v>
       </c>
@@ -1776,20 +1834,23 @@
       <c r="C17" s="2" t="s">
         <v>180</v>
       </c>
-      <c r="D17" s="5">
+      <c r="D17" s="8" t="s">
+        <v>188</v>
+      </c>
+      <c r="E17" s="5">
         <v>13</v>
       </c>
-      <c r="E17" s="5">
+      <c r="F17" s="5">
         <v>406</v>
       </c>
-      <c r="F17" s="4" t="s">
+      <c r="G17" s="4" t="s">
         <v>163</v>
       </c>
-      <c r="G17" s="2" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H17" s="2" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A18" s="3" t="s">
         <v>17</v>
       </c>
@@ -1799,20 +1860,23 @@
       <c r="C18" s="2" t="s">
         <v>180</v>
       </c>
-      <c r="D18" s="5">
+      <c r="D18" s="8" t="s">
+        <v>188</v>
+      </c>
+      <c r="E18" s="5">
         <v>10</v>
       </c>
-      <c r="E18" s="5">
+      <c r="F18" s="5">
         <v>167</v>
       </c>
-      <c r="F18" s="4" t="s">
+      <c r="G18" s="4" t="s">
         <v>164</v>
       </c>
-      <c r="G18" s="2" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H18" s="2" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A19" s="3" t="s">
         <v>18</v>
       </c>
@@ -1822,20 +1886,23 @@
       <c r="C19" s="8" t="s">
         <v>138</v>
       </c>
-      <c r="D19" s="5">
+      <c r="D19" s="8" t="s">
+        <v>188</v>
+      </c>
+      <c r="E19" s="5">
         <v>42</v>
       </c>
-      <c r="E19" s="5">
+      <c r="F19" s="5">
         <v>1070</v>
       </c>
-      <c r="F19" s="4" t="s">
+      <c r="G19" s="4" t="s">
         <v>156</v>
       </c>
-      <c r="G19" s="2" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7" ht="16.8" x14ac:dyDescent="0.3">
+      <c r="H19" s="2" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A20" s="3" t="s">
         <v>19</v>
       </c>
@@ -1845,20 +1912,23 @@
       <c r="C20" s="8" t="s">
         <v>139</v>
       </c>
-      <c r="D20" s="5">
+      <c r="D20" s="8" t="s">
+        <v>188</v>
+      </c>
+      <c r="E20" s="5">
         <v>150</v>
       </c>
-      <c r="E20" s="5">
+      <c r="F20" s="5">
         <v>2461</v>
       </c>
-      <c r="F20" s="4" t="s">
+      <c r="G20" s="4" t="s">
         <v>165</v>
       </c>
-      <c r="G20" s="2" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H20" s="2" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A21" s="3" t="s">
         <v>20</v>
       </c>
@@ -1868,20 +1938,23 @@
       <c r="C21" s="8" t="s">
         <v>140</v>
       </c>
-      <c r="D21" s="5">
+      <c r="D21" s="8" t="s">
+        <v>188</v>
+      </c>
+      <c r="E21" s="5">
         <v>31</v>
       </c>
-      <c r="E21" s="5">
+      <c r="F21" s="5">
         <v>915</v>
       </c>
-      <c r="F21" s="4" t="s">
+      <c r="G21" s="4" t="s">
         <v>166</v>
       </c>
-      <c r="G21" s="2" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H21" s="2" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A22" s="3" t="s">
         <v>21</v>
       </c>
@@ -1891,20 +1964,23 @@
       <c r="C22" s="2" t="s">
         <v>180</v>
       </c>
-      <c r="D22" s="5">
+      <c r="D22" s="8" t="s">
+        <v>188</v>
+      </c>
+      <c r="E22" s="5">
         <v>12</v>
       </c>
-      <c r="E22" s="5">
+      <c r="F22" s="5">
         <v>222</v>
       </c>
-      <c r="F22" s="4" t="s">
+      <c r="G22" s="4" t="s">
         <v>164</v>
       </c>
-      <c r="G22" s="2" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H22" s="2" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A23" s="3" t="s">
         <v>22</v>
       </c>
@@ -1914,20 +1990,23 @@
       <c r="C23" s="2" t="s">
         <v>180</v>
       </c>
-      <c r="D23" s="5">
+      <c r="D23" s="8" t="s">
+        <v>188</v>
+      </c>
+      <c r="E23" s="5">
         <v>8</v>
       </c>
-      <c r="E23" s="5">
+      <c r="F23" s="5">
         <v>117</v>
       </c>
-      <c r="F23" s="4" t="s">
+      <c r="G23" s="4" t="s">
         <v>157</v>
       </c>
-      <c r="G23" s="2" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H23" s="2" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A24" s="3" t="s">
         <v>23</v>
       </c>
@@ -1937,20 +2016,23 @@
       <c r="C24" s="8" t="s">
         <v>141</v>
       </c>
-      <c r="D24" s="5">
+      <c r="D24" s="8" t="s">
+        <v>188</v>
+      </c>
+      <c r="E24" s="5">
         <v>66</v>
       </c>
-      <c r="E24" s="5">
+      <c r="F24" s="5">
         <v>1292</v>
       </c>
-      <c r="F24" s="4" t="s">
+      <c r="G24" s="4" t="s">
         <v>167</v>
       </c>
-      <c r="G24" s="2" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H24" s="2" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A25" s="3" t="s">
         <v>24</v>
       </c>
@@ -1960,20 +2042,23 @@
       <c r="C25" s="8" t="s">
         <v>136</v>
       </c>
-      <c r="D25" s="5">
+      <c r="D25" s="8" t="s">
+        <v>188</v>
+      </c>
+      <c r="E25" s="5">
         <v>52</v>
       </c>
-      <c r="E25" s="5">
+      <c r="F25" s="5">
         <v>1364</v>
       </c>
-      <c r="F25" s="4" t="s">
+      <c r="G25" s="4" t="s">
         <v>168</v>
       </c>
-      <c r="G25" s="2" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H25" s="2" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A26" s="3" t="s">
         <v>25</v>
       </c>
@@ -1983,20 +2068,23 @@
       <c r="C26" s="2" t="s">
         <v>180</v>
       </c>
-      <c r="D26" s="5">
+      <c r="D26" s="8" t="s">
+        <v>188</v>
+      </c>
+      <c r="E26" s="5">
         <v>5</v>
       </c>
-      <c r="E26" s="5">
+      <c r="F26" s="5">
         <v>154</v>
       </c>
-      <c r="F26" s="4" t="s">
+      <c r="G26" s="4" t="s">
         <v>169</v>
       </c>
-      <c r="G26" s="2" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H26" s="2" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A27" s="3" t="s">
         <v>26</v>
       </c>
@@ -2006,20 +2094,23 @@
       <c r="C27" s="8" t="s">
         <v>142</v>
       </c>
-      <c r="D27" s="5">
+      <c r="D27" s="8" t="s">
+        <v>188</v>
+      </c>
+      <c r="E27" s="5">
         <v>48</v>
       </c>
-      <c r="E27" s="5">
+      <c r="F27" s="5">
         <v>1273</v>
       </c>
-      <c r="F27" s="4" t="s">
+      <c r="G27" s="4" t="s">
         <v>167</v>
       </c>
-      <c r="G27" s="2" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H27" s="2" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A28" s="3" t="s">
         <v>27</v>
       </c>
@@ -2029,20 +2120,23 @@
       <c r="C28" s="8" t="s">
         <v>143</v>
       </c>
-      <c r="D28" s="5">
+      <c r="D28" s="8" t="s">
+        <v>188</v>
+      </c>
+      <c r="E28" s="5">
         <v>12</v>
       </c>
-      <c r="E28" s="5">
+      <c r="F28" s="5">
         <v>357</v>
       </c>
-      <c r="F28" s="4" t="s">
+      <c r="G28" s="4" t="s">
         <v>170</v>
       </c>
-      <c r="G28" s="2" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H28" s="2" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A29" s="3" t="s">
         <v>28</v>
       </c>
@@ -2052,20 +2146,23 @@
       <c r="C29" s="2" t="s">
         <v>180</v>
       </c>
-      <c r="D29" s="5">
+      <c r="D29" s="8" t="s">
+        <v>188</v>
+      </c>
+      <c r="E29" s="5">
         <v>14</v>
       </c>
-      <c r="E29" s="5">
+      <c r="F29" s="5">
         <v>197</v>
       </c>
-      <c r="F29" s="4" t="s">
+      <c r="G29" s="4" t="s">
         <v>164</v>
       </c>
-      <c r="G29" s="2" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H29" s="2" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A30" s="3" t="s">
         <v>29</v>
       </c>
@@ -2075,20 +2172,23 @@
       <c r="C30" s="2" t="s">
         <v>180</v>
       </c>
-      <c r="D30" s="5">
+      <c r="D30" s="8" t="s">
+        <v>188</v>
+      </c>
+      <c r="E30" s="5">
         <v>3</v>
       </c>
-      <c r="E30" s="5">
+      <c r="F30" s="5">
         <v>73</v>
       </c>
-      <c r="F30" s="4" t="s">
+      <c r="G30" s="4" t="s">
         <v>157</v>
       </c>
-      <c r="G30" s="2" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H30" s="2" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A31" s="3" t="s">
         <v>30</v>
       </c>
@@ -2098,20 +2198,23 @@
       <c r="C31" s="2" t="s">
         <v>180</v>
       </c>
-      <c r="D31" s="5">
+      <c r="D31" s="8" t="s">
+        <v>188</v>
+      </c>
+      <c r="E31" s="5">
         <v>9</v>
       </c>
-      <c r="E31" s="5">
+      <c r="F31" s="5">
         <v>146</v>
       </c>
-      <c r="F31" s="4" t="s">
+      <c r="G31" s="4" t="s">
         <v>171</v>
       </c>
-      <c r="G31" s="2" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H31" s="2" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A32" s="3" t="s">
         <v>31</v>
       </c>
@@ -2121,20 +2224,23 @@
       <c r="C32" s="2" t="s">
         <v>180</v>
       </c>
-      <c r="D32" s="5">
+      <c r="D32" s="8" t="s">
+        <v>188</v>
+      </c>
+      <c r="E32" s="5">
         <v>1</v>
       </c>
-      <c r="E32" s="5">
+      <c r="F32" s="5">
         <v>21</v>
       </c>
-      <c r="F32" s="4" t="s">
+      <c r="G32" s="4" t="s">
         <v>172</v>
       </c>
-      <c r="G32" s="2" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H32" s="2" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A33" s="3" t="s">
         <v>32</v>
       </c>
@@ -2144,20 +2250,23 @@
       <c r="C33" s="2" t="s">
         <v>180</v>
       </c>
-      <c r="D33" s="5">
+      <c r="D33" s="8" t="s">
+        <v>188</v>
+      </c>
+      <c r="E33" s="5">
         <v>4</v>
       </c>
-      <c r="E33" s="5">
+      <c r="F33" s="5">
         <v>48</v>
       </c>
-      <c r="F33" s="4" t="s">
+      <c r="G33" s="4" t="s">
         <v>173</v>
       </c>
-      <c r="G33" s="2" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H33" s="2" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="34" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A34" s="3" t="s">
         <v>33</v>
       </c>
@@ -2167,20 +2276,23 @@
       <c r="C34" s="2" t="s">
         <v>180</v>
       </c>
-      <c r="D34" s="5">
+      <c r="D34" s="8" t="s">
+        <v>188</v>
+      </c>
+      <c r="E34" s="5">
         <v>7</v>
       </c>
-      <c r="E34" s="5">
+      <c r="F34" s="5">
         <v>105</v>
       </c>
-      <c r="F34" s="4" t="s">
+      <c r="G34" s="4" t="s">
         <v>169</v>
       </c>
-      <c r="G34" s="2" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H34" s="2" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="35" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A35" s="3" t="s">
         <v>34</v>
       </c>
@@ -2190,20 +2302,23 @@
       <c r="C35" s="2" t="s">
         <v>180</v>
       </c>
-      <c r="D35" s="5">
+      <c r="D35" s="8" t="s">
+        <v>188</v>
+      </c>
+      <c r="E35" s="5">
         <v>3</v>
       </c>
-      <c r="E35" s="5">
+      <c r="F35" s="5">
         <v>47</v>
       </c>
-      <c r="F35" s="4" t="s">
+      <c r="G35" s="4" t="s">
         <v>173</v>
       </c>
-      <c r="G35" s="2" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H35" s="2" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="36" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A36" s="3" t="s">
         <v>35</v>
       </c>
@@ -2213,20 +2328,23 @@
       <c r="C36" s="2" t="s">
         <v>180</v>
       </c>
-      <c r="D36" s="5">
+      <c r="D36" s="8" t="s">
+        <v>188</v>
+      </c>
+      <c r="E36" s="5">
         <v>3</v>
       </c>
-      <c r="E36" s="5">
+      <c r="F36" s="5">
         <v>46</v>
       </c>
-      <c r="F36" s="4" t="s">
+      <c r="G36" s="4" t="s">
         <v>173</v>
       </c>
-      <c r="G36" s="2" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H36" s="2" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="37" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A37" s="3" t="s">
         <v>36</v>
       </c>
@@ -2236,20 +2354,23 @@
       <c r="C37" s="2" t="s">
         <v>180</v>
       </c>
-      <c r="D37" s="5">
+      <c r="D37" s="8" t="s">
+        <v>188</v>
+      </c>
+      <c r="E37" s="5">
         <v>3</v>
       </c>
-      <c r="E37" s="5">
+      <c r="F37" s="5">
         <v>53</v>
       </c>
-      <c r="F37" s="4" t="s">
+      <c r="G37" s="4" t="s">
         <v>173</v>
       </c>
-      <c r="G37" s="2" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H37" s="2" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="38" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A38" s="3" t="s">
         <v>37</v>
       </c>
@@ -2259,20 +2380,23 @@
       <c r="C38" s="2" t="s">
         <v>180</v>
       </c>
-      <c r="D38" s="5">
+      <c r="D38" s="8" t="s">
+        <v>188</v>
+      </c>
+      <c r="E38" s="5">
         <v>2</v>
       </c>
-      <c r="E38" s="5">
+      <c r="F38" s="5">
         <v>38</v>
       </c>
-      <c r="F38" s="4" t="s">
+      <c r="G38" s="4" t="s">
         <v>172</v>
       </c>
-      <c r="G38" s="2" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H38" s="2" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="39" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A39" s="3" t="s">
         <v>38</v>
       </c>
@@ -2282,20 +2406,23 @@
       <c r="C39" s="2" t="s">
         <v>180</v>
       </c>
-      <c r="D39" s="5">
+      <c r="D39" s="8" t="s">
+        <v>188</v>
+      </c>
+      <c r="E39" s="5">
         <v>14</v>
       </c>
-      <c r="E39" s="5">
+      <c r="F39" s="5">
         <v>211</v>
       </c>
-      <c r="F39" s="4" t="s">
+      <c r="G39" s="4" t="s">
         <v>174</v>
       </c>
-      <c r="G39" s="2" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H39" s="2" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="40" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A40" s="3" t="s">
         <v>39</v>
       </c>
@@ -2305,20 +2432,23 @@
       <c r="C40" s="2" t="s">
         <v>180</v>
       </c>
-      <c r="D40" s="5">
+      <c r="D40" s="8" t="s">
+        <v>188</v>
+      </c>
+      <c r="E40" s="5">
         <v>4</v>
       </c>
-      <c r="E40" s="5">
+      <c r="F40" s="5">
         <v>55</v>
       </c>
-      <c r="F40" s="5">
+      <c r="G40" s="5">
         <v>10</v>
       </c>
-      <c r="G40" s="2" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H40" s="2" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="41" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A41" s="3" t="s">
         <v>40</v>
       </c>
@@ -2328,20 +2458,23 @@
       <c r="C41" s="8" t="s">
         <v>144</v>
       </c>
-      <c r="D41" s="5">
+      <c r="D41" s="8" t="s">
+        <v>189</v>
+      </c>
+      <c r="E41" s="5">
         <v>28</v>
       </c>
-      <c r="E41" s="5">
+      <c r="F41" s="5">
         <v>1071</v>
       </c>
-      <c r="F41" s="4" t="s">
+      <c r="G41" s="4" t="s">
         <v>160</v>
       </c>
-      <c r="G41" s="2" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H41" s="2" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="42" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A42" s="3" t="s">
         <v>41</v>
       </c>
@@ -2351,20 +2484,23 @@
       <c r="C42" s="8" t="s">
         <v>145</v>
       </c>
-      <c r="D42" s="5">
+      <c r="D42" s="8" t="s">
+        <v>189</v>
+      </c>
+      <c r="E42" s="5">
         <v>16</v>
       </c>
-      <c r="E42" s="5">
+      <c r="F42" s="5">
         <v>678</v>
       </c>
-      <c r="F42" s="4" t="s">
+      <c r="G42" s="4" t="s">
         <v>175</v>
       </c>
-      <c r="G42" s="2" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H42" s="2" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="43" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A43" s="3" t="s">
         <v>42</v>
       </c>
@@ -2374,20 +2510,23 @@
       <c r="C43" s="8" t="s">
         <v>146</v>
       </c>
-      <c r="D43" s="5">
+      <c r="D43" s="8" t="s">
+        <v>189</v>
+      </c>
+      <c r="E43" s="5">
         <v>24</v>
       </c>
-      <c r="E43" s="5">
+      <c r="F43" s="5">
         <v>1151</v>
       </c>
-      <c r="F43" s="4" t="s">
+      <c r="G43" s="4" t="s">
         <v>176</v>
       </c>
-      <c r="G43" s="2" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H43" s="2" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="44" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A44" s="3" t="s">
         <v>43</v>
       </c>
@@ -2397,20 +2536,23 @@
       <c r="C44" s="8" t="s">
         <v>147</v>
       </c>
-      <c r="D44" s="5">
+      <c r="D44" s="8" t="s">
+        <v>189</v>
+      </c>
+      <c r="E44" s="5">
         <v>21</v>
       </c>
-      <c r="E44" s="5">
+      <c r="F44" s="5">
         <v>879</v>
       </c>
-      <c r="F44" s="4" t="s">
+      <c r="G44" s="4" t="s">
         <v>155</v>
       </c>
-      <c r="G44" s="2" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H44" s="2" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="45" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A45" s="3" t="s">
         <v>44</v>
       </c>
@@ -2420,20 +2562,23 @@
       <c r="C45" s="8" t="s">
         <v>146</v>
       </c>
-      <c r="D45" s="5">
+      <c r="D45" s="8" t="s">
+        <v>189</v>
+      </c>
+      <c r="E45" s="5">
         <v>28</v>
       </c>
-      <c r="E45" s="5">
+      <c r="F45" s="5">
         <v>1007</v>
       </c>
-      <c r="F45" s="4" t="s">
+      <c r="G45" s="4" t="s">
         <v>177</v>
       </c>
-      <c r="G45" s="2" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H45" s="2" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="46" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A46" s="3" t="s">
         <v>45</v>
       </c>
@@ -2443,20 +2588,23 @@
       <c r="C46" s="8" t="s">
         <v>148</v>
       </c>
-      <c r="D46" s="5">
+      <c r="D46" s="8" t="s">
+        <v>189</v>
+      </c>
+      <c r="E46" s="5">
         <v>16</v>
       </c>
-      <c r="E46" s="5">
+      <c r="F46" s="5">
         <v>433</v>
       </c>
-      <c r="F46" s="4" t="s">
+      <c r="G46" s="4" t="s">
         <v>178</v>
       </c>
-      <c r="G46" s="2" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="47" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H46" s="2" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="47" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A47" s="3" t="s">
         <v>46</v>
       </c>
@@ -2466,20 +2614,23 @@
       <c r="C47" s="2" t="s">
         <v>180</v>
       </c>
-      <c r="D47" s="5">
+      <c r="D47" s="8" t="s">
+        <v>189</v>
+      </c>
+      <c r="E47" s="5">
         <v>16</v>
       </c>
-      <c r="E47" s="5">
+      <c r="F47" s="5">
         <v>437</v>
       </c>
-      <c r="F47" s="4" t="s">
+      <c r="G47" s="4" t="s">
         <v>178</v>
       </c>
-      <c r="G47" s="2" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="48" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H47" s="2" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="48" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A48" s="3" t="s">
         <v>47</v>
       </c>
@@ -2489,20 +2640,23 @@
       <c r="C48" s="2" t="s">
         <v>180</v>
       </c>
-      <c r="D48" s="5">
+      <c r="D48" s="8" t="s">
+        <v>189</v>
+      </c>
+      <c r="E48" s="5">
         <v>13</v>
       </c>
-      <c r="E48" s="5">
+      <c r="F48" s="5">
         <v>257</v>
       </c>
-      <c r="F48" s="4" t="s">
+      <c r="G48" s="4" t="s">
         <v>174</v>
       </c>
-      <c r="G48" s="2" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="49" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H48" s="2" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="49" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A49" s="3" t="s">
         <v>48</v>
       </c>
@@ -2512,20 +2666,23 @@
       <c r="C49" s="2" t="s">
         <v>180</v>
       </c>
-      <c r="D49" s="5">
+      <c r="D49" s="8" t="s">
+        <v>189</v>
+      </c>
+      <c r="E49" s="5">
         <v>6</v>
       </c>
-      <c r="E49" s="5">
+      <c r="F49" s="5">
         <v>149</v>
       </c>
-      <c r="F49" s="4" t="s">
+      <c r="G49" s="4" t="s">
         <v>169</v>
       </c>
-      <c r="G49" s="2" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="50" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H49" s="2" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="50" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A50" s="3" t="s">
         <v>49</v>
       </c>
@@ -2535,20 +2692,23 @@
       <c r="C50" s="2" t="s">
         <v>180</v>
       </c>
-      <c r="D50" s="5">
+      <c r="D50" s="8" t="s">
+        <v>189</v>
+      </c>
+      <c r="E50" s="5">
         <v>6</v>
       </c>
-      <c r="E50" s="5">
+      <c r="F50" s="5">
         <v>155</v>
       </c>
-      <c r="F50" s="4" t="s">
+      <c r="G50" s="4" t="s">
         <v>169</v>
       </c>
-      <c r="G50" s="2" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="51" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H50" s="2" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="51" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A51" s="3" t="s">
         <v>50</v>
       </c>
@@ -2558,20 +2718,23 @@
       <c r="C51" s="2" t="s">
         <v>180</v>
       </c>
-      <c r="D51" s="5">
+      <c r="D51" s="8" t="s">
+        <v>189</v>
+      </c>
+      <c r="E51" s="5">
         <v>4</v>
       </c>
-      <c r="E51" s="5">
+      <c r="F51" s="5">
         <v>104</v>
       </c>
-      <c r="F51" s="4" t="s">
+      <c r="G51" s="4" t="s">
         <v>157</v>
       </c>
-      <c r="G51" s="2" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="52" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H51" s="2" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="52" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A52" s="3" t="s">
         <v>51</v>
       </c>
@@ -2581,20 +2744,23 @@
       <c r="C52" s="2" t="s">
         <v>180</v>
       </c>
-      <c r="D52" s="5">
+      <c r="D52" s="8" t="s">
+        <v>189</v>
+      </c>
+      <c r="E52" s="5">
         <v>4</v>
       </c>
-      <c r="E52" s="5">
+      <c r="F52" s="5">
         <v>95</v>
       </c>
-      <c r="F52" s="4" t="s">
+      <c r="G52" s="4" t="s">
         <v>157</v>
       </c>
-      <c r="G52" s="2" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="53" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H52" s="2" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="53" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A53" s="3" t="s">
         <v>52</v>
       </c>
@@ -2604,20 +2770,23 @@
       <c r="C53" s="2" t="s">
         <v>180</v>
       </c>
-      <c r="D53" s="5">
+      <c r="D53" s="8" t="s">
+        <v>189</v>
+      </c>
+      <c r="E53" s="5">
         <v>5</v>
       </c>
-      <c r="E53" s="5">
+      <c r="F53" s="5">
         <v>89</v>
       </c>
-      <c r="F53" s="4" t="s">
+      <c r="G53" s="4" t="s">
         <v>173</v>
       </c>
-      <c r="G53" s="2" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="54" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H53" s="2" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="54" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A54" s="3" t="s">
         <v>53</v>
       </c>
@@ -2627,20 +2796,23 @@
       <c r="C54" s="2" t="s">
         <v>180</v>
       </c>
-      <c r="D54" s="5">
+      <c r="D54" s="8" t="s">
+        <v>189</v>
+      </c>
+      <c r="E54" s="5">
         <v>3</v>
       </c>
-      <c r="E54" s="5">
+      <c r="F54" s="5">
         <v>47</v>
       </c>
-      <c r="F54" s="4" t="s">
+      <c r="G54" s="4" t="s">
         <v>173</v>
       </c>
-      <c r="G54" s="2" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="55" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H54" s="2" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="55" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A55" s="3" t="s">
         <v>54</v>
       </c>
@@ -2650,20 +2822,23 @@
       <c r="C55" s="2" t="s">
         <v>180</v>
       </c>
-      <c r="D55" s="5">
+      <c r="D55" s="8" t="s">
+        <v>189</v>
+      </c>
+      <c r="E55" s="5">
         <v>6</v>
       </c>
-      <c r="E55" s="5">
+      <c r="F55" s="5">
         <v>113</v>
       </c>
-      <c r="F55" s="4" t="s">
+      <c r="G55" s="4" t="s">
         <v>157</v>
       </c>
-      <c r="G55" s="2" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="56" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H55" s="2" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="56" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A56" s="3" t="s">
         <v>55</v>
       </c>
@@ -2673,20 +2848,23 @@
       <c r="C56" s="2" t="s">
         <v>180</v>
       </c>
-      <c r="D56" s="5">
+      <c r="D56" s="8" t="s">
+        <v>189</v>
+      </c>
+      <c r="E56" s="5">
         <v>4</v>
       </c>
-      <c r="E56" s="5">
+      <c r="F56" s="5">
         <v>83</v>
       </c>
-      <c r="F56" s="4" t="s">
+      <c r="G56" s="4" t="s">
         <v>157</v>
       </c>
-      <c r="G56" s="2" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="57" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H56" s="2" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="57" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A57" s="3" t="s">
         <v>56</v>
       </c>
@@ -2696,20 +2874,23 @@
       <c r="C57" s="2" t="s">
         <v>180</v>
       </c>
-      <c r="D57" s="5">
+      <c r="D57" s="8" t="s">
+        <v>189</v>
+      </c>
+      <c r="E57" s="5">
         <v>3</v>
       </c>
-      <c r="E57" s="5">
+      <c r="F57" s="5">
         <v>46</v>
       </c>
-      <c r="F57" s="4" t="s">
+      <c r="G57" s="4" t="s">
         <v>173</v>
       </c>
-      <c r="G57" s="2" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="58" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H57" s="2" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="58" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A58" s="3" t="s">
         <v>57</v>
       </c>
@@ -2719,20 +2900,23 @@
       <c r="C58" s="2" t="s">
         <v>180</v>
       </c>
-      <c r="D58" s="5">
+      <c r="D58" s="8" t="s">
+        <v>189</v>
+      </c>
+      <c r="E58" s="5">
         <v>1</v>
       </c>
-      <c r="E58" s="5">
+      <c r="F58" s="5">
         <v>25</v>
       </c>
-      <c r="F58" s="4" t="s">
+      <c r="G58" s="4" t="s">
         <v>172</v>
       </c>
-      <c r="G58" s="2" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="59" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H58" s="2" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="59" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A59" s="3" t="s">
         <v>58</v>
       </c>
@@ -2742,20 +2926,23 @@
       <c r="C59" s="2" t="s">
         <v>180</v>
       </c>
-      <c r="D59" s="5">
+      <c r="D59" s="8" t="s">
+        <v>189</v>
+      </c>
+      <c r="E59" s="5">
         <v>13</v>
       </c>
-      <c r="E59" s="5">
+      <c r="F59" s="5">
         <v>303</v>
       </c>
-      <c r="F59" s="4" t="s">
+      <c r="G59" s="4" t="s">
         <v>179</v>
       </c>
-      <c r="G59" s="2" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="60" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H59" s="2" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="60" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A60" s="3" t="s">
         <v>59</v>
       </c>
@@ -2765,20 +2952,23 @@
       <c r="C60" s="8" t="s">
         <v>149</v>
       </c>
-      <c r="D60" s="5">
+      <c r="D60" s="8" t="s">
+        <v>189</v>
+      </c>
+      <c r="E60" s="5">
         <v>5</v>
       </c>
-      <c r="E60" s="5">
+      <c r="F60" s="5">
         <v>108</v>
       </c>
-      <c r="F60" s="4" t="s">
+      <c r="G60" s="4" t="s">
         <v>157</v>
       </c>
-      <c r="G60" s="2" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="61" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H60" s="2" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="61" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A61" s="3" t="s">
         <v>60</v>
       </c>
@@ -2788,20 +2978,23 @@
       <c r="C61" s="8" t="s">
         <v>150</v>
       </c>
-      <c r="D61" s="5">
+      <c r="D61" s="8" t="s">
+        <v>189</v>
+      </c>
+      <c r="E61" s="5">
         <v>5</v>
       </c>
-      <c r="E61" s="5">
+      <c r="F61" s="5">
         <v>105</v>
       </c>
-      <c r="F61" s="4" t="s">
+      <c r="G61" s="4" t="s">
         <v>157</v>
       </c>
-      <c r="G61" s="2" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="62" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H61" s="2" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="62" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A62" s="3" t="s">
         <v>61</v>
       </c>
@@ -2811,20 +3004,23 @@
       <c r="C62" s="2" t="s">
         <v>180</v>
       </c>
-      <c r="D62" s="5">
+      <c r="D62" s="8" t="s">
+        <v>189</v>
+      </c>
+      <c r="E62" s="5">
         <v>3</v>
       </c>
-      <c r="E62" s="5">
+      <c r="F62" s="5">
         <v>61</v>
       </c>
-      <c r="F62" s="4" t="s">
+      <c r="G62" s="4" t="s">
         <v>173</v>
       </c>
-      <c r="G62" s="2" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="63" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H62" s="2" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="63" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A63" s="3" t="s">
         <v>62</v>
       </c>
@@ -2834,20 +3030,23 @@
       <c r="C63" s="8" t="s">
         <v>147</v>
       </c>
-      <c r="D63" s="5">
+      <c r="D63" s="8" t="s">
+        <v>189</v>
+      </c>
+      <c r="E63" s="5">
         <v>5</v>
       </c>
-      <c r="E63" s="5">
+      <c r="F63" s="5">
         <v>104</v>
       </c>
-      <c r="F63" s="4" t="s">
+      <c r="G63" s="4" t="s">
         <v>157</v>
       </c>
-      <c r="G63" s="2" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="64" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H63" s="2" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="64" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A64" s="3" t="s">
         <v>63</v>
       </c>
@@ -2857,20 +3056,23 @@
       <c r="C64" s="2" t="s">
         <v>180</v>
       </c>
-      <c r="D64" s="5">
+      <c r="D64" s="8" t="s">
+        <v>189</v>
+      </c>
+      <c r="E64" s="5">
         <v>1</v>
       </c>
-      <c r="E64" s="5">
+      <c r="F64" s="5">
         <v>13</v>
       </c>
-      <c r="F64" s="4" t="s">
+      <c r="G64" s="4" t="s">
         <v>172</v>
       </c>
-      <c r="G64" s="2" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="65" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H64" s="2" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="65" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A65" s="3" t="s">
         <v>64</v>
       </c>
@@ -2880,20 +3082,23 @@
       <c r="C65" s="2" t="s">
         <v>180</v>
       </c>
-      <c r="D65" s="5">
+      <c r="D65" s="8" t="s">
+        <v>189</v>
+      </c>
+      <c r="E65" s="5">
         <v>1</v>
       </c>
-      <c r="E65" s="5">
+      <c r="F65" s="5">
         <v>14</v>
       </c>
-      <c r="F65" s="4" t="s">
+      <c r="G65" s="4" t="s">
         <v>172</v>
       </c>
-      <c r="G65" s="2" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="66" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H65" s="2" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="66" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A66" s="3" t="s">
         <v>65</v>
       </c>
@@ -2903,20 +3108,23 @@
       <c r="C66" s="8" t="s">
         <v>151</v>
       </c>
-      <c r="D66" s="5">
+      <c r="D66" s="8" t="s">
+        <v>189</v>
+      </c>
+      <c r="E66" s="5">
         <v>1</v>
       </c>
-      <c r="E66" s="5">
+      <c r="F66" s="5">
         <v>25</v>
       </c>
-      <c r="F66" s="4" t="s">
+      <c r="G66" s="4" t="s">
         <v>172</v>
       </c>
-      <c r="G66" s="2" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="67" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H66" s="2" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="67" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A67" s="3" t="s">
         <v>66</v>
       </c>
@@ -2926,16 +3134,19 @@
       <c r="C67" s="8" t="s">
         <v>147</v>
       </c>
-      <c r="D67" s="5">
+      <c r="D67" s="8" t="s">
+        <v>189</v>
+      </c>
+      <c r="E67" s="5">
         <v>22</v>
       </c>
-      <c r="E67" s="5">
+      <c r="F67" s="5">
         <v>404</v>
       </c>
-      <c r="F67" s="4" t="s">
+      <c r="G67" s="4" t="s">
         <v>170</v>
       </c>
-      <c r="G67" s="2" t="s">
+      <c r="H67" s="2" t="s">
         <v>180</v>
       </c>
     </row>
